--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.85.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.85.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.85.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0085.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0085.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,16 +609,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L72: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: of any subsÃ©quent stage of the cause, the plaintiff seems</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE " PRO CONFESSO."</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]PROCEEDINGS TO HEAR CAUSE " PRO CONFESSO."</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 0</t>
@@ -634,7 +638,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L96: line starts with punctuation glued to text :: .In cases where a decree is not absolute under order</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tunity to Court within the time specified in such notice, or that such</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -674,10 +678,14 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+5143 CJK UNIFIED IDEOGRAPH-5143 | isolated marker/symbol line :: (元)</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ tunity to Court within the time specified in such notice, or that such</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tunity to Court within the time specified in such notice, or that such</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -691,7 +699,11 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L96: line starts with punctuation glued to text :: .In cases where a decree is not absolute under order</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -721,7 +733,11 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
@@ -750,7 +766,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -965,7 +981,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -985,7 +1001,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L72: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1013,7 +1029,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1028,7 +1044,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: 0</t>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+5143 CJK UNIFIED IDEOGRAPH-5143 | isolated marker/symbol line :: (元)</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1051,7 +1067,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1071,7 +1087,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: .</t>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1114,7 +1130,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: -</t>
+          <t>L136: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1142,7 +1158,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1155,7 +1171,11 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>L137: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
@@ -1194,7 +1214,11 @@
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>L138: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
